--- a/artfynd/A 17228-2026 artfynd.xlsx
+++ b/artfynd/A 17228-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,6 +807,236 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132686168</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91925</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sjölund, Sjölund, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>596979</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6520558</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132686170</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sjölund, Sjölund, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>596956</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6520612</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Plantor</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17228-2026 artfynd.xlsx
+++ b/artfynd/A 17228-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -813,7 +813,7 @@
         <v>132686168</v>
       </c>
       <c r="B3" t="n">
-        <v>91925</v>
+        <v>91929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>132686170</v>
       </c>
       <c r="B4" t="n">
-        <v>99112</v>
+        <v>99116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,6 +1038,697 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132711137</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99116</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sjölund, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>596991</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6520590</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132711130</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99116</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sjölund, Sjölund, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>596991</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6520593</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132711133</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99116</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sjölund, Sjölund, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>596983</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6520605</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132711129</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99116</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sjölund, Sjölund, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>596993</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6520590</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132711135</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99116</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sjölund, Sjölund, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>596957</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6520601</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132711136</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99116</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sjölund, Sjölund, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>596934</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6520593</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17228-2026 artfynd.xlsx
+++ b/artfynd/A 17228-2026 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>132686168</v>
       </c>
       <c r="B3" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>132686170</v>
       </c>
       <c r="B4" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>132711137</v>
       </c>
       <c r="B5" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>132711130</v>
       </c>
       <c r="B6" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132711133</v>
       </c>
       <c r="B7" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>132711129</v>
       </c>
       <c r="B8" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>132711135</v>
       </c>
       <c r="B9" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>132711136</v>
       </c>
       <c r="B10" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 17228-2026 artfynd.xlsx
+++ b/artfynd/A 17228-2026 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>132686170</v>
       </c>
       <c r="B4" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>132711137</v>
       </c>
       <c r="B5" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>132711130</v>
       </c>
       <c r="B6" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132711133</v>
       </c>
       <c r="B7" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>132711129</v>
       </c>
       <c r="B8" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>132711135</v>
       </c>
       <c r="B9" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>132711136</v>
       </c>
       <c r="B10" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 17228-2026 artfynd.xlsx
+++ b/artfynd/A 17228-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1729,6 +1729,122 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132818989</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sjölund, Sjölund, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>597025</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6520570</v>
+      </c>
+      <c r="S11" t="n">
+        <v>18</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flera hundratal inom 15 meter</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Birgitta Hamstedt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17228-2026 artfynd.xlsx
+++ b/artfynd/A 17228-2026 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>132686168</v>
       </c>
       <c r="B3" t="n">
-        <v>91930</v>
+        <v>91931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>132686170</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>132711137</v>
       </c>
       <c r="B5" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>132711130</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132711133</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>132711129</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>132711135</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>132711136</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>132818989</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 17228-2026 artfynd.xlsx
+++ b/artfynd/A 17228-2026 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>132686168</v>
       </c>
       <c r="B3" t="n">
-        <v>91931</v>
+        <v>91933</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>132686170</v>
       </c>
       <c r="B4" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>132711137</v>
       </c>
       <c r="B5" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>132711130</v>
       </c>
       <c r="B6" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132711133</v>
       </c>
       <c r="B7" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>132711129</v>
       </c>
       <c r="B8" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>132711135</v>
       </c>
       <c r="B9" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>132711136</v>
       </c>
       <c r="B10" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>132818989</v>
       </c>
       <c r="B11" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 17228-2026 artfynd.xlsx
+++ b/artfynd/A 17228-2026 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>132686168</v>
       </c>
       <c r="B3" t="n">
-        <v>91933</v>
+        <v>91934</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>132686170</v>
       </c>
       <c r="B4" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>132711137</v>
       </c>
       <c r="B5" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>132711130</v>
       </c>
       <c r="B6" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132711133</v>
       </c>
       <c r="B7" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>132711129</v>
       </c>
       <c r="B8" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>132711135</v>
       </c>
       <c r="B9" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>132711136</v>
       </c>
       <c r="B10" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>132818989</v>
       </c>
       <c r="B11" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 17228-2026 artfynd.xlsx
+++ b/artfynd/A 17228-2026 artfynd.xlsx
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 17228-2026 artfynd.xlsx
+++ b/artfynd/A 17228-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3064127</v>
+        <v>132791692</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sjölund, Srm</t>
+          <t>Sjölund , Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597062.4011020777</v>
+        <v>596927</v>
       </c>
       <c r="R2" t="n">
-        <v>6520540.697593817</v>
+        <v>6520550</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,29 +742,14 @@
           <t>Stigtomta</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>D-Nyk-0272</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-08-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-08-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,32 +763,28 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>D-län Floraväktarna</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>D-län Floraväktarna</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Rolf Olsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132686168</v>
+        <v>1153117</v>
       </c>
       <c r="B3" t="n">
-        <v>91939</v>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,40 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjölund, Sjölund, Srm</t>
+          <t>Ö Sjölund (09H4a10), Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596979</v>
+        <v>596971</v>
       </c>
       <c r="R3" t="n">
-        <v>6520558</v>
+        <v>6520575</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,22 +846,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2004-12-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2004-12-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>090740101 / HYD AURC / Enstaka-sparsam (1)  / OBJ.AREA:2,2 ha</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,54 +871,53 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132686170</v>
+        <v>132686168</v>
       </c>
       <c r="B4" t="n">
-        <v>99130</v>
+        <v>91995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,13 +925,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596956</v>
+        <v>596979</v>
       </c>
       <c r="R4" t="n">
-        <v>6520612</v>
+        <v>6520558</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Plantor</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,52 +997,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132711137</v>
+        <v>112198714</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>110078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sjölund, Srm</t>
+          <t>Sjölund 300m OSO, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596991</v>
+        <v>597046</v>
       </c>
       <c r="R5" t="n">
-        <v>6520590</v>
+        <v>6520506</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,22 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:36</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:36</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,28 +1080,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Skogsbryn</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132711130</v>
+        <v>3017447</v>
       </c>
       <c r="B6" t="n">
-        <v>99130</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,28 +1132,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sjölund, Sjölund, Srm</t>
+          <t>Ö Sjölund (09H4a10), Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596991</v>
+        <v>596971</v>
       </c>
       <c r="R6" t="n">
-        <v>6520593</v>
+        <v>6520575</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,27 +1169,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:12</t>
+          <t>2004-12-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:12</t>
+          <t>2004-12-06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Uppskattat antal</t>
+          <t>090740101 / GOOD REP / Enstaka-sparsam (1)  / OBJ.AREA:2,2 ha</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,22 +1194,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132711133</v>
+        <v>3064128</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,26 +1240,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sjölund, Sjölund, Srm</t>
+          <t>Sjölund, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596983</v>
+        <v>597062</v>
       </c>
       <c r="R7" t="n">
-        <v>6520605</v>
+        <v>6520541</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,24 +1282,19 @@
           <t>Stigtomta</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D-Nyk-0272</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:40</t>
+          <t>2012-08-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:40</t>
+          <t>2012-08-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,26 +1305,35 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>D-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>D-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132711129</v>
+        <v>132686170</v>
       </c>
       <c r="B8" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1360,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1429,13 +1373,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596993</v>
+        <v>596956</v>
       </c>
       <c r="R8" t="n">
-        <v>6520590</v>
+        <v>6520612</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,22 +1403,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Plantor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,17 +1443,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132711135</v>
+        <v>132711129</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1480,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1544,13 +1493,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596957</v>
+        <v>596993</v>
       </c>
       <c r="R9" t="n">
-        <v>6520601</v>
+        <v>6520590</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1579,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132711136</v>
+        <v>132711130</v>
       </c>
       <c r="B10" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1595,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1659,13 +1608,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596934</v>
+        <v>596991</v>
       </c>
       <c r="R10" t="n">
         <v>6520593</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1694,7 +1643,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1704,7 +1653,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132818989</v>
+        <v>132711133</v>
       </c>
       <c r="B11" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1713,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1770,13 +1728,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597025</v>
+        <v>596983</v>
       </c>
       <c r="R11" t="n">
-        <v>6520570</v>
+        <v>6520605</v>
       </c>
       <c r="S11" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1800,27 +1758,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Flera hundratal inom 15 meter</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,10 +1793,782 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132711135</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sjölund, Sjölund, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>596957</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6520601</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132711136</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sjölund, Sjölund, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>596934</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6520593</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132711137</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sjölund, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>596991</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6520590</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132818989</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sjölund, Sjölund, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>597025</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6520570</v>
+      </c>
+      <c r="S15" t="n">
+        <v>18</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flera hundratal inom 15 meter</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
           <t>Göran Ekström, Birgitta Hamstedt</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132770933</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sjölund, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>596969</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6520588</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rolf Olsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132791632</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sjölund , Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>596927</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6520550</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rolf Olsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132771352</v>
+      </c>
+      <c r="B18" t="n">
+        <v>103908</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>225103</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vanlig sälg</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sjölund 300m OSO, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>597046</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6520506</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Skogsbryn</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rolf Olsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17228-2026 artfynd.xlsx
+++ b/artfynd/A 17228-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132791692</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1153117</t>
         </is>
       </c>
     </row>
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132686168</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112198714</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3017447</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,6 +1355,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3064128</t>
         </is>
       </c>
     </row>
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132686170</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1562,6 +1602,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132711129</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1682,6 +1727,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132711130</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1797,6 +1847,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132711133</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,6 +1967,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132711135</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2027,6 +2087,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132711136</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2138,6 +2203,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132711137</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2254,6 +2324,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132818989</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2360,6 +2435,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132770933</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2466,6 +2546,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132791632</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2569,8 +2654,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132771352</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>